--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_64_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_64_IN_Piura.xlsx
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>22.76</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>35.76</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>33.9</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>7.59</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>35.7738</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>20.9334</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>58.52</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>14.8404</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>41.48</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>35.7804</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2267,6 +2267,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2384,6 +2385,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2428,6 +2430,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="168" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2911,11 +2914,11 @@
       </c>
       <c r="B20" s="33">
         <f>SUM(B10:B19)</f>
-        <v/>
+        <v>552.18</v>
       </c>
       <c r="C20" s="23">
         <f>SUM(C10:C19)</f>
-        <v/>
+        <v>99.98</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -2925,19 +2928,19 @@
       <c r="E20" s="17" t="inlineStr"/>
       <c r="F20" s="17">
         <f>ROUND(AVERAGE(F10:F19),2)</f>
-        <v/>
+        <v>29.09</v>
       </c>
       <c r="G20" s="22">
         <f>ROUND(AVERAGE(G10:G19),4)</f>
-        <v/>
+        <v>0.6292</v>
       </c>
       <c r="H20" s="23">
         <f>ROUND(AVERAGE(H10:H19),2)</f>
-        <v/>
+        <v>93.19</v>
       </c>
       <c r="I20" s="23">
         <f>ROUND(AVERAGE(I10:I19),2)</f>
-        <v/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="21"/>
